--- a/lead_generation_forms/024_sales_discovery_questionnaire--lead_generation_forms.xlsx
+++ b/lead_generation_forms/024_sales_discovery_questionnaire--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
